--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ151"/>
+  <dimension ref="A1:AZ152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14014,10 +14014,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>93088717</v>
+        <v>136993027</v>
       </c>
       <c r="B126" t="n">
-        <v>97990</v>
+        <v>106502</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14025,19 +14025,23 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>224358</v>
+        <v>221144</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr"/>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
@@ -14045,14 +14049,14 @@
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Normyrarna, Vrm</t>
+          <t>Bäckelbergsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>411694</v>
+        <v>412051</v>
       </c>
       <c r="R126" t="n">
-        <v>6707193</v>
+        <v>6707453</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14079,12 +14083,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14100,68 +14104,65 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Jonatan Axelsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Jonatan Axelsson, Rob Nil</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93088717</t>
+          <t>https://artportalen.se/Sighting/136993027</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>108975982</v>
+        <v>93088717</v>
       </c>
       <c r="B127" t="n">
-        <v>79085</v>
+        <v>97990</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>224358</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vanlig plattlummer</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
+          <t>Lycopodium complanatum subsp. complanatum</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Söder Bäckelbergssätern, Vrm</t>
+          <t>Normyrarna, Vrm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>411766</v>
+        <v>411694</v>
       </c>
       <c r="R127" t="n">
-        <v>6707189</v>
+        <v>6707193</v>
       </c>
       <c r="S127" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14185,12 +14186,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2021-05-05</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2021-05-05</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14206,24 +14207,24 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108975982</t>
+          <t>https://artportalen.se/Sighting/93088717</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>115259147</v>
+        <v>108975982</v>
       </c>
       <c r="B128" t="n">
         <v>79085</v>
@@ -14257,17 +14258,17 @@
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Söder Bäckelbergssätern, Vrm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>411842</v>
+        <v>411766</v>
       </c>
       <c r="R128" t="n">
-        <v>6707254</v>
+        <v>6707189</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14291,12 +14292,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14312,24 +14313,24 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Svea Nikula, Malin Henell, Albin Tengius, Julia Lea Falk, Amanda Rudelius</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115259147</t>
+          <t>https://artportalen.se/Sighting/108975982</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>117368504</v>
+        <v>115259147</v>
       </c>
       <c r="B129" t="n">
         <v>79085</v>
@@ -14363,14 +14364,14 @@
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Sydost Bäckelberget, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>412693</v>
+        <v>411842</v>
       </c>
       <c r="R129" t="n">
-        <v>6708020</v>
+        <v>6707254</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14397,12 +14398,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14418,24 +14419,24 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>August Oljeqvist, Svea Nikula, Malin Henell, Albin Tengius, Julia Lea Falk, Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117368504</t>
+          <t>https://artportalen.se/Sighting/115259147</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>117486531</v>
+        <v>117368504</v>
       </c>
       <c r="B130" t="n">
         <v>79085</v>
@@ -14469,14 +14470,14 @@
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Sydost Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>412681</v>
+        <v>412693</v>
       </c>
       <c r="R130" t="n">
-        <v>6708233</v>
+        <v>6708020</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14503,12 +14504,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14524,24 +14525,24 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117486531</t>
+          <t>https://artportalen.se/Sighting/117368504</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>117486616</v>
+        <v>117486531</v>
       </c>
       <c r="B131" t="n">
         <v>79085</v>
@@ -14579,10 +14580,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>412692</v>
+        <v>412681</v>
       </c>
       <c r="R131" t="n">
-        <v>6708159</v>
+        <v>6708233</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14635,19 +14636,19 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Iris Elmér, Carl Teg, Anton Björk, August Oljeqvist</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117486616</t>
+          <t>https://artportalen.se/Sighting/117486531</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>117486800</v>
+        <v>117486616</v>
       </c>
       <c r="B132" t="n">
         <v>79085</v>
@@ -14685,10 +14686,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>412596</v>
+        <v>412692</v>
       </c>
       <c r="R132" t="n">
-        <v>6708194</v>
+        <v>6708159</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14741,19 +14742,19 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Iris Elmér, Carl Teg, Anton Björk, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117486800</t>
+          <t>https://artportalen.se/Sighting/117486616</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>117486832</v>
+        <v>117486800</v>
       </c>
       <c r="B133" t="n">
         <v>79085</v>
@@ -14791,10 +14792,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>412569</v>
+        <v>412596</v>
       </c>
       <c r="R133" t="n">
-        <v>6708173</v>
+        <v>6708194</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14853,13 +14854,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117486832</t>
+          <t>https://artportalen.se/Sighting/117486800</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>117486865</v>
+        <v>117486832</v>
       </c>
       <c r="B134" t="n">
         <v>79085</v>
@@ -14897,10 +14898,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>412572</v>
+        <v>412569</v>
       </c>
       <c r="R134" t="n">
-        <v>6708145</v>
+        <v>6708173</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14959,13 +14960,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117486865</t>
+          <t>https://artportalen.se/Sighting/117486832</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>117486935</v>
+        <v>117486865</v>
       </c>
       <c r="B135" t="n">
         <v>79085</v>
@@ -15003,10 +15004,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>412553</v>
+        <v>412572</v>
       </c>
       <c r="R135" t="n">
-        <v>6708107</v>
+        <v>6708145</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15065,13 +15066,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117486935</t>
+          <t>https://artportalen.se/Sighting/117486865</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>117486983</v>
+        <v>117486935</v>
       </c>
       <c r="B136" t="n">
         <v>79085</v>
@@ -15109,10 +15110,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>412620</v>
+        <v>412553</v>
       </c>
       <c r="R136" t="n">
-        <v>6708033</v>
+        <v>6708107</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15171,13 +15172,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117486983</t>
+          <t>https://artportalen.se/Sighting/117486935</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>117490696</v>
+        <v>117486983</v>
       </c>
       <c r="B137" t="n">
         <v>79085</v>
@@ -15211,17 +15212,17 @@
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>412626</v>
+        <v>412620</v>
       </c>
       <c r="R137" t="n">
-        <v>6708158</v>
+        <v>6708033</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15266,24 +15267,24 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117490696</t>
+          <t>https://artportalen.se/Sighting/117486983</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>117490817</v>
+        <v>117490696</v>
       </c>
       <c r="B138" t="n">
         <v>79085</v>
@@ -15321,10 +15322,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>412566</v>
+        <v>412626</v>
       </c>
       <c r="R138" t="n">
-        <v>6708147</v>
+        <v>6708158</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -15377,19 +15378,19 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Carl Teg, Anton Björk, August Oljeqvist, Iris Elmér</t>
+          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117490817</t>
+          <t>https://artportalen.se/Sighting/117490696</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>117495323</v>
+        <v>117490817</v>
       </c>
       <c r="B139" t="n">
         <v>79085</v>
@@ -15418,16 +15419,19 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>412559</v>
+        <v>412566</v>
       </c>
       <c r="R139" t="n">
-        <v>6708064</v>
+        <v>6708147</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -15468,30 +15472,31 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>Carl Teg, Anton Björk, August Oljeqvist, Iris Elmér</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117495323</t>
+          <t>https://artportalen.se/Sighting/117490817</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>117495329</v>
+        <v>117495323</v>
       </c>
       <c r="B140" t="n">
         <v>79085</v>
@@ -15526,10 +15531,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>412504</v>
+        <v>412559</v>
       </c>
       <c r="R140" t="n">
-        <v>6708038</v>
+        <v>6708064</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -15587,13 +15592,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117495329</t>
+          <t>https://artportalen.se/Sighting/117495323</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120020795</v>
+        <v>117495329</v>
       </c>
       <c r="B141" t="n">
         <v>79085</v>
@@ -15622,22 +15627,19 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>411952</v>
+        <v>412504</v>
       </c>
       <c r="R141" t="n">
-        <v>6707419</v>
+        <v>6708038</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15661,12 +15663,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15675,7 +15677,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15687,19 +15688,19 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120020795</t>
+          <t>https://artportalen.se/Sighting/117495329</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120054966</v>
+        <v>120020795</v>
       </c>
       <c r="B142" t="n">
         <v>79085</v>
@@ -15728,19 +15729,22 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>411714</v>
+        <v>411952</v>
       </c>
       <c r="R142" t="n">
-        <v>6707352</v>
+        <v>6707419</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15764,12 +15768,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15778,6 +15782,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15795,13 +15800,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120054966</t>
+          <t>https://artportalen.se/Sighting/120020795</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128646627</v>
+        <v>120054966</v>
       </c>
       <c r="B143" t="n">
         <v>79085</v>
@@ -15832,17 +15837,17 @@
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>411752</v>
+        <v>411714</v>
       </c>
       <c r="R143" t="n">
-        <v>6707112</v>
+        <v>6707352</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15866,12 +15871,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15886,65 +15891,62 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128646627</t>
+          <t>https://artportalen.se/Sighting/120054966</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>115259355</v>
+        <v>128646627</v>
       </c>
       <c r="B144" t="n">
-        <v>80392</v>
+        <v>79085</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>411999</v>
+        <v>411752</v>
       </c>
       <c r="R144" t="n">
-        <v>6707402</v>
+        <v>6707112</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15971,12 +15973,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15985,31 +15987,30 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Svea Nikula, Malin Henell, Albin Tengius, Julia Lea Falk, Amanda Rudelius</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115259355</t>
+          <t>https://artportalen.se/Sighting/128646627</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>117368432</v>
+        <v>115259355</v>
       </c>
       <c r="B145" t="n">
         <v>80392</v>
@@ -16043,17 +16044,17 @@
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Bäckelbergssätern, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>412175</v>
+        <v>411999</v>
       </c>
       <c r="R145" t="n">
-        <v>6707731</v>
+        <v>6707402</v>
       </c>
       <c r="S145" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16077,12 +16078,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16098,24 +16099,24 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>August Oljeqvist, Svea Nikula, Malin Henell, Albin Tengius, Julia Lea Falk, Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117368432</t>
+          <t>https://artportalen.se/Sighting/115259355</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>117490620</v>
+        <v>117368432</v>
       </c>
       <c r="B146" t="n">
         <v>80392</v>
@@ -16149,17 +16150,17 @@
       <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelbergssätern, Vrm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>412636</v>
+        <v>412175</v>
       </c>
       <c r="R146" t="n">
-        <v>6708175</v>
+        <v>6707731</v>
       </c>
       <c r="S146" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16183,12 +16184,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16201,42 +16202,27 @@
       <c r="AG146" t="b">
         <v>0</v>
       </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117490620</t>
+          <t>https://artportalen.se/Sighting/117368432</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120020731</v>
+        <v>117490620</v>
       </c>
       <c r="B147" t="n">
         <v>80392</v>
@@ -16270,17 +16256,17 @@
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>412004</v>
+        <v>412636</v>
       </c>
       <c r="R147" t="n">
-        <v>6707384</v>
+        <v>6708175</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16304,12 +16290,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16322,27 +16308,42 @@
       <c r="AG147" t="b">
         <v>0</v>
       </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120020731</t>
+          <t>https://artportalen.se/Sighting/117490620</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128646636</v>
+        <v>120020731</v>
       </c>
       <c r="B148" t="n">
         <v>80392</v>
@@ -16371,16 +16372,19 @@
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>411774</v>
+        <v>412004</v>
       </c>
       <c r="R148" t="n">
-        <v>6707536</v>
+        <v>6707384</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16407,12 +16411,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16421,74 +16425,72 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128646636</t>
+          <t>https://artportalen.se/Sighting/120020731</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>115813460</v>
+        <v>128646636</v>
       </c>
       <c r="B149" t="n">
-        <v>75356</v>
+        <v>80392</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>229654</v>
+        <v>229497</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>411641</v>
+        <v>411774</v>
       </c>
       <c r="R149" t="n">
-        <v>6707359</v>
+        <v>6707536</v>
       </c>
       <c r="S149" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16512,50 +16514,44 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Under utredning.</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF149" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115813460</t>
+          <t>https://artportalen.se/Sighting/128646636</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>115968638</v>
+        <v>115813460</v>
       </c>
       <c r="B150" t="n">
         <v>75356</v>
@@ -16593,13 +16589,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>411603</v>
+        <v>411641</v>
       </c>
       <c r="R150" t="n">
-        <v>6707373</v>
+        <v>6707359</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16623,44 +16619,29 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>På skrovellav vid grov sälg samt på flertalet grankvistar strax intill. Även vid bålar på blocket som sälgen växer på. Förekomst på minst 45 bålar spridda på de olika träden och blocket. Växer tillsammans med lunglav och stuplav i sänka mellan vägen och bäcken.  Tidigare fynd (rapporterat som skrovellav med apothecier).</t>
+          <t>Under utredning.</t>
         </is>
       </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>skrovellav</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
@@ -16675,13 +16656,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115968638</t>
+          <t>https://artportalen.se/Sighting/115813460</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>124716294</v>
+        <v>115968638</v>
       </c>
       <c r="B151" t="n">
         <v>75356</v>
@@ -16715,14 +16696,14 @@
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Bäckelbergssätern, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>411609</v>
+        <v>411603</v>
       </c>
       <c r="R151" t="n">
-        <v>6707377</v>
+        <v>6707373</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16749,17 +16730,17 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Återfynd.</t>
+          <t>På skrovellav vid grov sälg samt på flertalet grankvistar strax intill. Även vid bålar på blocket som sälgen växer på. Förekomst på minst 45 bålar spridda på de olika träden och blocket. Växer tillsammans med lunglav och stuplav i sänka mellan vägen och bäcken.  Tidigare fynd (rapporterat som skrovellav med apothecier).</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16790,16 +16771,142 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Johan Svedholm</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Johan Svedholm</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115968638</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>124716294</v>
+      </c>
+      <c r="B152" t="n">
+        <v>75356</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>229654</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Skrovellavsknapp</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Plectocarpon scrobiculatae</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Diederich &amp; Etayo</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Bäckelbergssätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>411609</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6707377</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Återfynd.</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>skrovellav</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Johan Svedholm</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Johan Svedholm</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/124716294</t>
         </is>
@@ -16957,6 +17064,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14017,7 +14017,7 @@
         <v>136993027</v>
       </c>
       <c r="B126" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14017,7 +14017,7 @@
         <v>136993027</v>
       </c>
       <c r="B126" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14017,7 +14017,7 @@
         <v>136993027</v>
       </c>
       <c r="B126" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14017,7 +14017,7 @@
         <v>136993027</v>
       </c>
       <c r="B126" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14017,7 +14017,7 @@
         <v>136993027</v>
       </c>
       <c r="B126" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14017,7 +14017,7 @@
         <v>136993027</v>
       </c>
       <c r="B126" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14017,7 +14017,7 @@
         <v>136993027</v>
       </c>
       <c r="B126" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14017,7 +14017,7 @@
         <v>136993027</v>
       </c>
       <c r="B126" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14017,7 +14017,7 @@
         <v>136993027</v>
       </c>
       <c r="B126" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14017,7 +14017,7 @@
         <v>136993027</v>
       </c>
       <c r="B126" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14017,7 +14017,7 @@
         <v>136993027</v>
       </c>
       <c r="B126" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14017,7 +14017,7 @@
         <v>136993027</v>
       </c>
       <c r="B126" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14017,7 +14017,7 @@
         <v>136993027</v>
       </c>
       <c r="B126" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14017,7 +14017,7 @@
         <v>136993027</v>
       </c>
       <c r="B126" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14017,7 +14017,7 @@
         <v>136993027</v>
       </c>
       <c r="B126" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14017,7 +14017,7 @@
         <v>136993027</v>
       </c>
       <c r="B126" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14017,7 +14017,7 @@
         <v>136993027</v>
       </c>
       <c r="B126" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14017,7 +14017,7 @@
         <v>136993027</v>
       </c>
       <c r="B126" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
